--- a/Exp3_PTO_GRPO/eda/results/method/contrast/tables/contrast.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/method/contrast/tables/contrast.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H271"/>
+  <dimension ref="A1:H289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4512,14 +4512,14 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>claude-haiku-4-5</t>
+          <t>gpt-4o-mini</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -4530,26 +4530,26 @@
         <v>96</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.0024</v>
+        <v>-0.3319</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.0038</v>
+        <v>-0.4368</v>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>claude-haiku-4-5</t>
+          <t>gpt-4o-mini</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4560,26 +4560,26 @@
         <v>96</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.0321</v>
+        <v>-0.1727</v>
       </c>
       <c r="G138" t="n">
-        <v>-0.0483</v>
+        <v>-0.3626</v>
       </c>
       <c r="H138" t="n">
-        <v>1</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>claude-haiku-4-5</t>
+          <t>gpt-4o-mini</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -4590,26 +4590,26 @@
         <v>96</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0339</v>
+        <v>-0.1536</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0482</v>
+        <v>-0.29</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>0.0398</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>claude-haiku-4-5</t>
+          <t>gpt-4o-mini</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -4620,26 +4620,26 @@
         <v>96</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.0278</v>
+        <v>-0.1962</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.0394</v>
+        <v>-0.2804</v>
       </c>
       <c r="H140" t="n">
-        <v>1</v>
+        <v>0.1161</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>claude-haiku-4-5</t>
+          <t>gpt-4o-mini</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -4650,26 +4650,26 @@
         <v>96</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.0182</v>
+        <v>-0.3698</v>
       </c>
       <c r="G141" t="n">
-        <v>-0.0353</v>
+        <v>-0.5505</v>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>claude-haiku-4-5</t>
+          <t>gpt-4o-mini</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -4680,26 +4680,26 @@
         <v>96</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.0258</v>
+        <v>-0.0622</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.1166</v>
+        <v>-0.3435</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>claude-haiku-4-5</t>
+          <t>gpt-4o-mini</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -4710,26 +4710,26 @@
         <v>96</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.0131</v>
+        <v>0.0391</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.0366</v>
+        <v>0.1669</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>0.2488</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>claude-haiku-4-5</t>
+          <t>gpt-4o-mini</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -4740,26 +4740,26 @@
         <v>96</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.0458</v>
+        <v>-0.3292</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.0619</v>
+        <v>-0.4043</v>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>0.0008</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>claude-haiku-4-5</t>
+          <t>gpt-4o-mini</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -4770,13 +4770,13 @@
         <v>96</v>
       </c>
       <c r="F145" t="n">
-        <v>0.0411</v>
+        <v>-0.3346</v>
       </c>
       <c r="G145" t="n">
-        <v>0.065</v>
+        <v>-0.4526</v>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -4789,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="C146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -4800,10 +4800,10 @@
         <v>96</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0925</v>
+        <v>-0.0024</v>
       </c>
       <c r="G146" t="n">
-        <v>0.1195</v>
+        <v>-0.0038</v>
       </c>
       <c r="H146" t="n">
         <v>1</v>
@@ -4819,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="C147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -4830,10 +4830,10 @@
         <v>96</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0148</v>
+        <v>-0.0321</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0194</v>
+        <v>-0.0483</v>
       </c>
       <c r="H147" t="n">
         <v>1</v>
@@ -4849,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="C148" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -4860,10 +4860,10 @@
         <v>96</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0833</v>
+        <v>0.0339</v>
       </c>
       <c r="G148" t="n">
-        <v>0.1014</v>
+        <v>0.0482</v>
       </c>
       <c r="H148" t="n">
         <v>1</v>
@@ -4879,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -4890,10 +4890,10 @@
         <v>96</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0573</v>
+        <v>-0.0278</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0757</v>
+        <v>-0.0394</v>
       </c>
       <c r="H149" t="n">
         <v>1</v>
@@ -4909,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         <v>96</v>
       </c>
       <c r="F150" t="n">
-        <v>0.026</v>
+        <v>-0.0182</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0487</v>
+        <v>-0.0353</v>
       </c>
       <c r="H150" t="n">
         <v>1</v>
@@ -4939,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -4950,10 +4950,10 @@
         <v>96</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.01</v>
+        <v>-0.0258</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.047</v>
+        <v>-0.1166</v>
       </c>
       <c r="H151" t="n">
         <v>1</v>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="C152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -4980,10 +4980,10 @@
         <v>96</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0368</v>
+        <v>-0.0131</v>
       </c>
       <c r="G152" t="n">
-        <v>0.09229999999999999</v>
+        <v>-0.0366</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="C153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -5010,10 +5010,10 @@
         <v>96</v>
       </c>
       <c r="F153" t="n">
-        <v>0.1083</v>
+        <v>-0.0458</v>
       </c>
       <c r="G153" t="n">
-        <v>0.1127</v>
+        <v>-0.0619</v>
       </c>
       <c r="H153" t="n">
         <v>1</v>
@@ -5029,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="C154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>96</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0766</v>
+        <v>0.0411</v>
       </c>
       <c r="G154" t="n">
-        <v>0.1091</v>
+        <v>0.065</v>
       </c>
       <c r="H154" t="n">
         <v>1</v>
@@ -5059,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -5070,13 +5070,13 @@
         <v>96</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.1564</v>
+        <v>0.0925</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.2781</v>
+        <v>0.1195</v>
       </c>
       <c r="H155" t="n">
-        <v>0.0612</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -5089,7 +5089,7 @@
         <v>0</v>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -5100,13 +5100,13 @@
         <v>96</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.2552</v>
+        <v>0.0148</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.4574</v>
+        <v>0.0194</v>
       </c>
       <c r="H156" t="n">
-        <v>0.0005</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -5119,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="C157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -5130,13 +5130,13 @@
         <v>96</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.1576</v>
+        <v>0.0833</v>
       </c>
       <c r="G157" t="n">
-        <v>-0.2653</v>
+        <v>0.1014</v>
       </c>
       <c r="H157" t="n">
-        <v>0.0922</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -5149,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -5160,13 +5160,13 @@
         <v>96</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.1389</v>
+        <v>0.0573</v>
       </c>
       <c r="G158" t="n">
-        <v>-0.282</v>
+        <v>0.0757</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1005</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -5179,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="C159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -5190,13 +5190,13 @@
         <v>96</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.1068</v>
+        <v>0.026</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.2154</v>
+        <v>0.0487</v>
       </c>
       <c r="H159" t="n">
-        <v>0.144</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -5209,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="C160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -5220,13 +5220,13 @@
         <v>96</v>
       </c>
       <c r="F160" t="n">
-        <v>-0.0289</v>
+        <v>-0.01</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.1515</v>
+        <v>-0.047</v>
       </c>
       <c r="H160" t="n">
-        <v>0.543</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -5239,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="C161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -5250,13 +5250,13 @@
         <v>96</v>
       </c>
       <c r="F161" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0368</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0265</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="H161" t="n">
-        <v>0.8385</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -5269,7 +5269,7 @@
         <v>0</v>
       </c>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -5280,13 +5280,13 @@
         <v>96</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.2104</v>
+        <v>0.1083</v>
       </c>
       <c r="G162" t="n">
-        <v>-0.2803</v>
+        <v>0.1127</v>
       </c>
       <c r="H162" t="n">
-        <v>0.06560000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -5299,7 +5299,7 @@
         <v>0</v>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -5310,13 +5310,13 @@
         <v>96</v>
       </c>
       <c r="F163" t="n">
-        <v>-0.1023</v>
+        <v>0.0766</v>
       </c>
       <c r="G163" t="n">
-        <v>-0.1981</v>
+        <v>0.1091</v>
       </c>
       <c r="H163" t="n">
-        <v>0.2958</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -5329,7 +5329,7 @@
         <v>0</v>
       </c>
       <c r="C164" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -5340,13 +5340,13 @@
         <v>96</v>
       </c>
       <c r="F164" t="n">
-        <v>0.13</v>
+        <v>-0.1564</v>
       </c>
       <c r="G164" t="n">
-        <v>0.1709</v>
+        <v>-0.2781</v>
       </c>
       <c r="H164" t="n">
-        <v>1</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="165">
@@ -5359,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -5370,13 +5370,13 @@
         <v>96</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.0234</v>
+        <v>-0.2552</v>
       </c>
       <c r="G165" t="n">
-        <v>-0.0363</v>
+        <v>-0.4574</v>
       </c>
       <c r="H165" t="n">
-        <v>1</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="166">
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="C166" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -5400,13 +5400,13 @@
         <v>96</v>
       </c>
       <c r="F166" t="n">
-        <v>0.1055</v>
+        <v>-0.1576</v>
       </c>
       <c r="G166" t="n">
-        <v>0.1495</v>
+        <v>-0.2653</v>
       </c>
       <c r="H166" t="n">
-        <v>1</v>
+        <v>0.0922</v>
       </c>
     </row>
     <row r="167">
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -5430,13 +5430,13 @@
         <v>96</v>
       </c>
       <c r="F167" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.1389</v>
       </c>
       <c r="G167" t="n">
-        <v>0.1442</v>
+        <v>-0.282</v>
       </c>
       <c r="H167" t="n">
-        <v>1</v>
+        <v>0.1005</v>
       </c>
     </row>
     <row r="168">
@@ -5449,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="C168" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -5460,13 +5460,13 @@
         <v>96</v>
       </c>
       <c r="F168" t="n">
-        <v>0.1172</v>
+        <v>-0.1068</v>
       </c>
       <c r="G168" t="n">
-        <v>0.2523</v>
+        <v>-0.2154</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1642</v>
+        <v>0.144</v>
       </c>
     </row>
     <row r="169">
@@ -5479,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -5490,13 +5490,13 @@
         <v>96</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.0092</v>
+        <v>-0.0289</v>
       </c>
       <c r="G169" t="n">
-        <v>-0.049</v>
+        <v>-0.1515</v>
       </c>
       <c r="H169" t="n">
-        <v>1</v>
+        <v>0.543</v>
       </c>
     </row>
     <row r="170">
@@ -5509,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="C170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -5520,13 +5520,13 @@
         <v>96</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.1183</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.4192</v>
+        <v>0.0265</v>
       </c>
       <c r="H170" t="n">
-        <v>0.0014</v>
+        <v>0.8385</v>
       </c>
     </row>
     <row r="171">
@@ -5539,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="C171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -5550,13 +5550,13 @@
         <v>96</v>
       </c>
       <c r="F171" t="n">
-        <v>0.1479</v>
+        <v>-0.2104</v>
       </c>
       <c r="G171" t="n">
-        <v>0.1583</v>
+        <v>-0.2803</v>
       </c>
       <c r="H171" t="n">
-        <v>1</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="172">
@@ -5569,7 +5569,7 @@
         <v>0</v>
       </c>
       <c r="C172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -5580,13 +5580,13 @@
         <v>96</v>
       </c>
       <c r="F172" t="n">
-        <v>0.1121</v>
+        <v>-0.1023</v>
       </c>
       <c r="G172" t="n">
-        <v>0.1608</v>
+        <v>-0.1981</v>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>0.2958</v>
       </c>
     </row>
     <row r="173">
@@ -5599,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="C173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -5610,13 +5610,13 @@
         <v>96</v>
       </c>
       <c r="F173" t="n">
-        <v>0.2654</v>
+        <v>0.13</v>
       </c>
       <c r="G173" t="n">
-        <v>0.3549</v>
+        <v>0.1709</v>
       </c>
       <c r="H173" t="n">
-        <v>0.0141</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -5629,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="C174" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>96</v>
       </c>
       <c r="F174" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.0234</v>
       </c>
       <c r="G174" t="n">
-        <v>0.157</v>
+        <v>-0.0363</v>
       </c>
       <c r="H174" t="n">
-        <v>0.2329</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -5659,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="C175" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -5670,13 +5670,13 @@
         <v>96</v>
       </c>
       <c r="F175" t="n">
-        <v>0.1107</v>
+        <v>0.1055</v>
       </c>
       <c r="G175" t="n">
-        <v>0.1847</v>
+        <v>0.1495</v>
       </c>
       <c r="H175" t="n">
-        <v>0.2329</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="C176" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -5700,13 +5700,13 @@
         <v>96</v>
       </c>
       <c r="F176" t="n">
-        <v>0.1076</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="G176" t="n">
-        <v>0.1807</v>
+        <v>0.1442</v>
       </c>
       <c r="H176" t="n">
-        <v>0.2329</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
@@ -5719,7 +5719,7 @@
         <v>0</v>
       </c>
       <c r="C177" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -5730,13 +5730,13 @@
         <v>96</v>
       </c>
       <c r="F177" t="n">
-        <v>0.2943</v>
+        <v>0.1172</v>
       </c>
       <c r="G177" t="n">
-        <v>0.6012999999999999</v>
+        <v>0.2523</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>0.1642</v>
       </c>
     </row>
     <row r="178">
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="C178" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -5760,13 +5760,13 @@
         <v>96</v>
       </c>
       <c r="F178" t="n">
-        <v>0.0282</v>
+        <v>-0.0092</v>
       </c>
       <c r="G178" t="n">
-        <v>0.1311</v>
+        <v>-0.049</v>
       </c>
       <c r="H178" t="n">
-        <v>0.2209</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="C179" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -5790,13 +5790,13 @@
         <v>96</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.1257</v>
+        <v>-0.1183</v>
       </c>
       <c r="G179" t="n">
-        <v>-0.3855</v>
+        <v>-0.4192</v>
       </c>
       <c r="H179" t="n">
-        <v>0.003</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="180">
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
       <c r="C180" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -5820,13 +5820,13 @@
         <v>96</v>
       </c>
       <c r="F180" t="n">
-        <v>0.2875</v>
+        <v>0.1479</v>
       </c>
       <c r="G180" t="n">
-        <v>0.317</v>
+        <v>0.1583</v>
       </c>
       <c r="H180" t="n">
-        <v>0.0274</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -5839,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -5850,13 +5850,13 @@
         <v>96</v>
       </c>
       <c r="F181" t="n">
-        <v>0.2433</v>
+        <v>0.1121</v>
       </c>
       <c r="G181" t="n">
-        <v>0.3347</v>
+        <v>0.1608</v>
       </c>
       <c r="H181" t="n">
-        <v>0.0227</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -5880,13 +5880,13 @@
         <v>96</v>
       </c>
       <c r="F182" t="n">
-        <v>0.479</v>
+        <v>0.2654</v>
       </c>
       <c r="G182" t="n">
-        <v>0.5215</v>
+        <v>0.3549</v>
       </c>
       <c r="H182" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="183">
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -5910,13 +5910,13 @@
         <v>96</v>
       </c>
       <c r="F183" t="n">
-        <v>0.1476</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="G183" t="n">
-        <v>0.2157</v>
+        <v>0.157</v>
       </c>
       <c r="H183" t="n">
-        <v>0.162</v>
+        <v>0.2329</v>
       </c>
     </row>
     <row r="184">
@@ -5929,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -5940,13 +5940,13 @@
         <v>96</v>
       </c>
       <c r="F184" t="n">
-        <v>0.2292</v>
+        <v>0.1107</v>
       </c>
       <c r="G184" t="n">
-        <v>0.3278</v>
+        <v>0.1847</v>
       </c>
       <c r="H184" t="n">
-        <v>0.0049</v>
+        <v>0.2329</v>
       </c>
     </row>
     <row r="185">
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -5970,13 +5970,13 @@
         <v>96</v>
       </c>
       <c r="F185" t="n">
-        <v>0.3351</v>
+        <v>0.1076</v>
       </c>
       <c r="G185" t="n">
-        <v>0.4459</v>
+        <v>0.1807</v>
       </c>
       <c r="H185" t="n">
-        <v>0.0004</v>
+        <v>0.2329</v>
       </c>
     </row>
     <row r="186">
@@ -5989,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>96</v>
       </c>
       <c r="F186" t="n">
-        <v>0.2682</v>
+        <v>0.2943</v>
       </c>
       <c r="G186" t="n">
-        <v>0.5226</v>
+        <v>0.6012999999999999</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="C187" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -6030,13 +6030,13 @@
         <v>96</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0583</v>
+        <v>0.0282</v>
       </c>
       <c r="G187" t="n">
-        <v>0.2811</v>
+        <v>0.1311</v>
       </c>
       <c r="H187" t="n">
-        <v>0.0581</v>
+        <v>0.2209</v>
       </c>
     </row>
     <row r="188">
@@ -6049,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -6060,13 +6060,13 @@
         <v>96</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.0302</v>
+        <v>-0.1257</v>
       </c>
       <c r="G188" t="n">
-        <v>-0.0847</v>
+        <v>-0.3855</v>
       </c>
       <c r="H188" t="n">
-        <v>0.4262</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="189">
@@ -6079,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -6090,13 +6090,13 @@
         <v>96</v>
       </c>
       <c r="F189" t="n">
-        <v>0.5812</v>
+        <v>0.2875</v>
       </c>
       <c r="G189" t="n">
-        <v>0.505</v>
+        <v>0.317</v>
       </c>
       <c r="H189" t="n">
-        <v>0.0002</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="190">
@@ -6109,7 +6109,7 @@
         <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -6120,13 +6120,13 @@
         <v>96</v>
       </c>
       <c r="F190" t="n">
-        <v>0.3768</v>
+        <v>0.2433</v>
       </c>
       <c r="G190" t="n">
-        <v>0.4742</v>
+        <v>0.3347</v>
       </c>
       <c r="H190" t="n">
-        <v>0.0002</v>
+        <v>0.0227</v>
       </c>
     </row>
     <row r="191">
@@ -6139,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -6150,13 +6150,13 @@
         <v>96</v>
       </c>
       <c r="F191" t="n">
-        <v>0.248</v>
+        <v>0.479</v>
       </c>
       <c r="G191" t="n">
-        <v>0.3256</v>
+        <v>0.5215</v>
       </c>
       <c r="H191" t="n">
-        <v>0.004</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="192">
@@ -6169,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -6180,13 +6180,13 @@
         <v>96</v>
       </c>
       <c r="F192" t="n">
-        <v>0.0582</v>
+        <v>0.1476</v>
       </c>
       <c r="G192" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.2157</v>
       </c>
       <c r="H192" t="n">
-        <v>0.6665</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="193">
@@ -6199,7 +6199,7 @@
         <v>0</v>
       </c>
       <c r="C193" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -6210,13 +6210,13 @@
         <v>96</v>
       </c>
       <c r="F193" t="n">
-        <v>0.1081</v>
+        <v>0.2292</v>
       </c>
       <c r="G193" t="n">
-        <v>0.1591</v>
+        <v>0.3278</v>
       </c>
       <c r="H193" t="n">
-        <v>0.3466</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="194">
@@ -6229,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="C194" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -6240,13 +6240,13 @@
         <v>96</v>
       </c>
       <c r="F194" t="n">
-        <v>0.1163</v>
+        <v>0.3351</v>
       </c>
       <c r="G194" t="n">
-        <v>0.1792</v>
+        <v>0.4459</v>
       </c>
       <c r="H194" t="n">
-        <v>0.3466</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="195">
@@ -6259,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="C195" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -6270,13 +6270,13 @@
         <v>96</v>
       </c>
       <c r="F195" t="n">
-        <v>0.1979</v>
+        <v>0.2682</v>
       </c>
       <c r="G195" t="n">
-        <v>0.4262</v>
+        <v>0.5226</v>
       </c>
       <c r="H195" t="n">
-        <v>0.0012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -6289,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="C196" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -6300,13 +6300,13 @@
         <v>96</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.0012</v>
+        <v>0.0583</v>
       </c>
       <c r="G196" t="n">
-        <v>-0.0059</v>
+        <v>0.2811</v>
       </c>
       <c r="H196" t="n">
-        <v>0.6665</v>
+        <v>0.0581</v>
       </c>
     </row>
     <row r="197">
@@ -6319,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="C197" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -6330,13 +6330,13 @@
         <v>96</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.0369</v>
+        <v>-0.0302</v>
       </c>
       <c r="G197" t="n">
-        <v>-0.1032</v>
+        <v>-0.0847</v>
       </c>
       <c r="H197" t="n">
-        <v>0.6665</v>
+        <v>0.4262</v>
       </c>
     </row>
     <row r="198">
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="C198" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -6360,13 +6360,13 @@
         <v>96</v>
       </c>
       <c r="F198" t="n">
-        <v>0.2688</v>
+        <v>0.5812</v>
       </c>
       <c r="G198" t="n">
-        <v>0.2997</v>
+        <v>0.505</v>
       </c>
       <c r="H198" t="n">
-        <v>0.0154</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="199">
@@ -6379,7 +6379,7 @@
         <v>0</v>
       </c>
       <c r="C199" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -6390,13 +6390,13 @@
         <v>96</v>
       </c>
       <c r="F199" t="n">
-        <v>0.2273</v>
+        <v>0.3768</v>
       </c>
       <c r="G199" t="n">
-        <v>0.3191</v>
+        <v>0.4742</v>
       </c>
       <c r="H199" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="200">
@@ -6409,7 +6409,7 @@
         <v>0</v>
       </c>
       <c r="C200" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -6420,13 +6420,13 @@
         <v>96</v>
       </c>
       <c r="F200" t="n">
-        <v>0.2783</v>
+        <v>0.248</v>
       </c>
       <c r="G200" t="n">
-        <v>0.4632</v>
+        <v>0.3256</v>
       </c>
       <c r="H200" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="201">
@@ -6439,7 +6439,7 @@
         <v>0</v>
       </c>
       <c r="C201" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -6450,13 +6450,13 @@
         <v>96</v>
       </c>
       <c r="F201" t="n">
-        <v>-0.0122</v>
+        <v>0.0582</v>
       </c>
       <c r="G201" t="n">
-        <v>-0.0223</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="H201" t="n">
-        <v>1</v>
+        <v>0.6665</v>
       </c>
     </row>
     <row r="202">
@@ -6469,7 +6469,7 @@
         <v>0</v>
       </c>
       <c r="C202" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -6480,13 +6480,13 @@
         <v>96</v>
       </c>
       <c r="F202" t="n">
-        <v>0.0898</v>
+        <v>0.1081</v>
       </c>
       <c r="G202" t="n">
-        <v>0.1629</v>
+        <v>0.1591</v>
       </c>
       <c r="H202" t="n">
-        <v>0.3752</v>
+        <v>0.3466</v>
       </c>
     </row>
     <row r="203">
@@ -6499,7 +6499,7 @@
         <v>0</v>
       </c>
       <c r="C203" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -6510,13 +6510,13 @@
         <v>96</v>
       </c>
       <c r="F203" t="n">
-        <v>0.1198</v>
+        <v>0.1163</v>
       </c>
       <c r="G203" t="n">
-        <v>0.2357</v>
+        <v>0.1792</v>
       </c>
       <c r="H203" t="n">
-        <v>0.0387</v>
+        <v>0.3466</v>
       </c>
     </row>
     <row r="204">
@@ -6529,7 +6529,7 @@
         <v>0</v>
       </c>
       <c r="C204" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -6540,13 +6540,13 @@
         <v>96</v>
       </c>
       <c r="F204" t="n">
-        <v>0.1745</v>
+        <v>0.1979</v>
       </c>
       <c r="G204" t="n">
-        <v>0.4906</v>
+        <v>0.4262</v>
       </c>
       <c r="H204" t="n">
-        <v>0.0001</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="205">
@@ -6559,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="C205" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -6570,13 +6570,13 @@
         <v>96</v>
       </c>
       <c r="F205" t="n">
-        <v>0.0091</v>
+        <v>-0.0012</v>
       </c>
       <c r="G205" t="n">
-        <v>0.044</v>
+        <v>-0.0059</v>
       </c>
       <c r="H205" t="n">
-        <v>1</v>
+        <v>0.6665</v>
       </c>
     </row>
     <row r="206">
@@ -6589,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="C206" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -6600,13 +6600,13 @@
         <v>96</v>
       </c>
       <c r="F206" t="n">
-        <v>-0.2272</v>
+        <v>-0.0369</v>
       </c>
       <c r="G206" t="n">
-        <v>-0.6324</v>
+        <v>-0.1032</v>
       </c>
       <c r="H206" t="n">
-        <v>0</v>
+        <v>0.6665</v>
       </c>
     </row>
     <row r="207">
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="C207" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -6630,13 +6630,13 @@
         <v>96</v>
       </c>
       <c r="F207" t="n">
-        <v>0.3979</v>
+        <v>0.2688</v>
       </c>
       <c r="G207" t="n">
-        <v>0.55</v>
+        <v>0.2997</v>
       </c>
       <c r="H207" t="n">
-        <v>0</v>
+        <v>0.0154</v>
       </c>
     </row>
     <row r="208">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -6660,13 +6660,13 @@
         <v>96</v>
       </c>
       <c r="F208" t="n">
-        <v>0.1587</v>
+        <v>0.2273</v>
       </c>
       <c r="G208" t="n">
-        <v>0.2638</v>
+        <v>0.3191</v>
       </c>
       <c r="H208" t="n">
-        <v>0.0167</v>
+        <v>0.009900000000000001</v>
       </c>
     </row>
     <row r="209">
@@ -6679,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="C209" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -6690,10 +6690,10 @@
         <v>96</v>
       </c>
       <c r="F209" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.2783</v>
       </c>
       <c r="G209" t="n">
-        <v>1.0829</v>
+        <v>0.4632</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="C210" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -6720,13 +6720,13 @@
         <v>96</v>
       </c>
       <c r="F210" t="n">
-        <v>0.6076</v>
+        <v>-0.0122</v>
       </c>
       <c r="G210" t="n">
-        <v>0.875</v>
+        <v>-0.0223</v>
       </c>
       <c r="H210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
@@ -6739,7 +6739,7 @@
         <v>0</v>
       </c>
       <c r="C211" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -6750,13 +6750,13 @@
         <v>96</v>
       </c>
       <c r="F211" t="n">
-        <v>0.7279</v>
+        <v>0.0898</v>
       </c>
       <c r="G211" t="n">
-        <v>1.1092</v>
+        <v>0.1629</v>
       </c>
       <c r="H211" t="n">
-        <v>0</v>
+        <v>0.3752</v>
       </c>
     </row>
     <row r="212">
@@ -6769,7 +6769,7 @@
         <v>0</v>
       </c>
       <c r="C212" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -6780,13 +6780,13 @@
         <v>96</v>
       </c>
       <c r="F212" t="n">
-        <v>0.7205</v>
+        <v>0.1198</v>
       </c>
       <c r="G212" t="n">
-        <v>1.0283</v>
+        <v>0.2357</v>
       </c>
       <c r="H212" t="n">
-        <v>0</v>
+        <v>0.0387</v>
       </c>
     </row>
     <row r="213">
@@ -6799,7 +6799,7 @@
         <v>0</v>
       </c>
       <c r="C213" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -6810,13 +6810,13 @@
         <v>96</v>
       </c>
       <c r="F213" t="n">
-        <v>0.4167</v>
+        <v>0.1745</v>
       </c>
       <c r="G213" t="n">
-        <v>0.9297</v>
+        <v>0.4906</v>
       </c>
       <c r="H213" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="214">
@@ -6829,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="C214" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -6840,13 +6840,13 @@
         <v>96</v>
       </c>
       <c r="F214" t="n">
-        <v>0.1745</v>
+        <v>0.0091</v>
       </c>
       <c r="G214" t="n">
-        <v>0.8273</v>
+        <v>0.044</v>
       </c>
       <c r="H214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -6859,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="C215" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -6870,13 +6870,13 @@
         <v>96</v>
       </c>
       <c r="F215" t="n">
-        <v>0.051</v>
+        <v>-0.2272</v>
       </c>
       <c r="G215" t="n">
-        <v>0.1243</v>
+        <v>-0.6324</v>
       </c>
       <c r="H215" t="n">
-        <v>0.1005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -6889,7 +6889,7 @@
         <v>0</v>
       </c>
       <c r="C216" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -6900,10 +6900,10 @@
         <v>96</v>
       </c>
       <c r="F216" t="n">
-        <v>1.0271</v>
+        <v>0.3979</v>
       </c>
       <c r="G216" t="n">
-        <v>1.0249</v>
+        <v>0.55</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="C217" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -6930,13 +6930,13 @@
         <v>96</v>
       </c>
       <c r="F217" t="n">
-        <v>0.8107</v>
+        <v>0.1587</v>
       </c>
       <c r="G217" t="n">
-        <v>1.0273</v>
+        <v>0.2638</v>
       </c>
       <c r="H217" t="n">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
     </row>
     <row r="218">
@@ -6949,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="C218" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>96</v>
       </c>
       <c r="F218" t="n">
-        <v>0.6089</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="G218" t="n">
-        <v>1.2652</v>
+        <v>1.0829</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6979,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="C219" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -6990,10 +6990,10 @@
         <v>96</v>
       </c>
       <c r="F219" t="n">
-        <v>0.2856</v>
+        <v>0.6076</v>
       </c>
       <c r="G219" t="n">
-        <v>0.4758</v>
+        <v>0.875</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -7009,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -7020,10 +7020,10 @@
         <v>96</v>
       </c>
       <c r="F220" t="n">
-        <v>0.3242</v>
+        <v>0.7279</v>
       </c>
       <c r="G220" t="n">
-        <v>0.6031</v>
+        <v>1.1092</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>0</v>
       </c>
       <c r="C221" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -7050,10 +7050,10 @@
         <v>96</v>
       </c>
       <c r="F221" t="n">
-        <v>0.2483</v>
+        <v>0.7205</v>
       </c>
       <c r="G221" t="n">
-        <v>0.5095</v>
+        <v>1.0283</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="C222" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -7080,10 +7080,10 @@
         <v>96</v>
       </c>
       <c r="F222" t="n">
-        <v>0.2526</v>
+        <v>0.4167</v>
       </c>
       <c r="G222" t="n">
-        <v>0.648</v>
+        <v>0.9297</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="C223" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -7110,13 +7110,13 @@
         <v>96</v>
       </c>
       <c r="F223" t="n">
-        <v>0.0207</v>
+        <v>0.1745</v>
       </c>
       <c r="G223" t="n">
-        <v>0.1219</v>
+        <v>0.8273</v>
       </c>
       <c r="H223" t="n">
-        <v>0.2036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -7129,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="C224" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -7140,13 +7140,13 @@
         <v>96</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.2245</v>
+        <v>0.051</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.6672</v>
+        <v>0.1243</v>
       </c>
       <c r="H224" t="n">
-        <v>0</v>
+        <v>0.1005</v>
       </c>
     </row>
     <row r="225">
@@ -7159,7 +7159,7 @@
         <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -7170,10 +7170,10 @@
         <v>96</v>
       </c>
       <c r="F225" t="n">
-        <v>0.7729</v>
+        <v>1.0271</v>
       </c>
       <c r="G225" t="n">
-        <v>1.2087</v>
+        <v>1.0249</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
         <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -7200,10 +7200,10 @@
         <v>96</v>
       </c>
       <c r="F226" t="n">
-        <v>0.4449</v>
+        <v>0.8107</v>
       </c>
       <c r="G226" t="n">
-        <v>0.9308999999999999</v>
+        <v>1.0273</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -7216,10 +7216,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C227" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>96</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.0347</v>
+        <v>0.6089</v>
       </c>
       <c r="G227" t="n">
-        <v>-0.043</v>
+        <v>1.2652</v>
       </c>
       <c r="H227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -7246,10 +7246,10 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -7260,13 +7260,13 @@
         <v>96</v>
       </c>
       <c r="F228" t="n">
-        <v>-0.0625</v>
+        <v>0.2856</v>
       </c>
       <c r="G228" t="n">
-        <v>-0.0853</v>
+        <v>0.4758</v>
       </c>
       <c r="H228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -7276,10 +7276,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -7290,13 +7290,13 @@
         <v>96</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.07290000000000001</v>
+        <v>0.3242</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.1009</v>
+        <v>0.6031</v>
       </c>
       <c r="H229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C230" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -7320,13 +7320,13 @@
         <v>96</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.0556</v>
+        <v>0.2483</v>
       </c>
       <c r="G230" t="n">
-        <v>-0.06950000000000001</v>
+        <v>0.5095</v>
       </c>
       <c r="H230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -7336,10 +7336,10 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -7350,13 +7350,13 @@
         <v>96</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.0391</v>
+        <v>0.2526</v>
       </c>
       <c r="G231" t="n">
-        <v>-0.0621</v>
+        <v>0.648</v>
       </c>
       <c r="H231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -7380,13 +7380,13 @@
         <v>96</v>
       </c>
       <c r="F232" t="n">
-        <v>0.0213</v>
+        <v>0.0207</v>
       </c>
       <c r="G232" t="n">
-        <v>0.1053</v>
+        <v>0.1219</v>
       </c>
       <c r="H232" t="n">
-        <v>1</v>
+        <v>0.2036</v>
       </c>
     </row>
     <row r="233">
@@ -7396,10 +7396,10 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -7410,13 +7410,13 @@
         <v>96</v>
       </c>
       <c r="F233" t="n">
-        <v>0.0351</v>
+        <v>-0.2245</v>
       </c>
       <c r="G233" t="n">
-        <v>0.08840000000000001</v>
+        <v>-0.6672</v>
       </c>
       <c r="H233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -7440,13 +7440,13 @@
         <v>96</v>
       </c>
       <c r="F234" t="n">
-        <v>-0.0125</v>
+        <v>0.7729</v>
       </c>
       <c r="G234" t="n">
-        <v>-0.0124</v>
+        <v>1.2087</v>
       </c>
       <c r="H234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -7470,13 +7470,13 @@
         <v>96</v>
       </c>
       <c r="F235" t="n">
-        <v>-0.057</v>
+        <v>0.4449</v>
       </c>
       <c r="G235" t="n">
-        <v>-0.0795</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="H235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -7489,7 +7489,7 @@
         <v>5</v>
       </c>
       <c r="C236" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -7500,10 +7500,10 @@
         <v>96</v>
       </c>
       <c r="F236" t="n">
-        <v>-0.0786</v>
+        <v>-0.0347</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.1134</v>
+        <v>-0.043</v>
       </c>
       <c r="H236" t="n">
         <v>1</v>
@@ -7519,7 +7519,7 @@
         <v>5</v>
       </c>
       <c r="C237" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -7530,10 +7530,10 @@
         <v>96</v>
       </c>
       <c r="F237" t="n">
-        <v>-0.026</v>
+        <v>-0.0625</v>
       </c>
       <c r="G237" t="n">
-        <v>-0.0331</v>
+        <v>-0.0853</v>
       </c>
       <c r="H237" t="n">
         <v>1</v>
@@ -7549,7 +7549,7 @@
         <v>5</v>
       </c>
       <c r="C238" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -7560,10 +7560,10 @@
         <v>96</v>
       </c>
       <c r="F238" t="n">
-        <v>-0.0078</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="G238" t="n">
-        <v>-0.0092</v>
+        <v>-0.1009</v>
       </c>
       <c r="H238" t="n">
         <v>1</v>
@@ -7579,7 +7579,7 @@
         <v>5</v>
       </c>
       <c r="C239" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -7590,10 +7590,10 @@
         <v>96</v>
       </c>
       <c r="F239" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0556</v>
       </c>
       <c r="G239" t="n">
-        <v>-0.0837</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="H239" t="n">
         <v>1</v>
@@ -7609,7 +7609,7 @@
         <v>5</v>
       </c>
       <c r="C240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -7620,13 +7620,13 @@
         <v>96</v>
       </c>
       <c r="F240" t="n">
-        <v>-0.125</v>
+        <v>-0.0391</v>
       </c>
       <c r="G240" t="n">
-        <v>-0.2003</v>
+        <v>-0.0621</v>
       </c>
       <c r="H240" t="n">
-        <v>0.306</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -7639,7 +7639,7 @@
         <v>5</v>
       </c>
       <c r="C241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -7650,10 +7650,10 @@
         <v>96</v>
       </c>
       <c r="F241" t="n">
-        <v>-0.0028</v>
+        <v>0.0213</v>
       </c>
       <c r="G241" t="n">
-        <v>-0.0127</v>
+        <v>0.1053</v>
       </c>
       <c r="H241" t="n">
         <v>1</v>
@@ -7669,7 +7669,7 @@
         <v>5</v>
       </c>
       <c r="C242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -7680,10 +7680,10 @@
         <v>96</v>
       </c>
       <c r="F242" t="n">
-        <v>0.0377</v>
+        <v>0.0351</v>
       </c>
       <c r="G242" t="n">
-        <v>0.0935</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="H242" t="n">
         <v>1</v>
@@ -7699,7 +7699,7 @@
         <v>5</v>
       </c>
       <c r="C243" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -7710,10 +7710,10 @@
         <v>96</v>
       </c>
       <c r="F243" t="n">
-        <v>-0.0646</v>
+        <v>-0.0125</v>
       </c>
       <c r="G243" t="n">
-        <v>-0.0766</v>
+        <v>-0.0124</v>
       </c>
       <c r="H243" t="n">
         <v>1</v>
@@ -7729,7 +7729,7 @@
         <v>5</v>
       </c>
       <c r="C244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -7740,10 +7740,10 @@
         <v>96</v>
       </c>
       <c r="F244" t="n">
-        <v>-0.0925</v>
+        <v>-0.057</v>
       </c>
       <c r="G244" t="n">
-        <v>-0.1455</v>
+        <v>-0.0795</v>
       </c>
       <c r="H244" t="n">
         <v>1</v>
@@ -7759,7 +7759,7 @@
         <v>5</v>
       </c>
       <c r="C245" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -7770,13 +7770,13 @@
         <v>96</v>
       </c>
       <c r="F245" t="n">
-        <v>-0.236</v>
+        <v>-0.0786</v>
       </c>
       <c r="G245" t="n">
-        <v>-0.3628</v>
+        <v>-0.1134</v>
       </c>
       <c r="H245" t="n">
-        <v>0.0051</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -7789,7 +7789,7 @@
         <v>5</v>
       </c>
       <c r="C246" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -7800,13 +7800,13 @@
         <v>96</v>
       </c>
       <c r="F246" t="n">
-        <v>-0.2057</v>
+        <v>-0.026</v>
       </c>
       <c r="G246" t="n">
-        <v>-0.3413</v>
+        <v>-0.0331</v>
       </c>
       <c r="H246" t="n">
-        <v>0.0114</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -7819,7 +7819,7 @@
         <v>5</v>
       </c>
       <c r="C247" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -7830,13 +7830,13 @@
         <v>96</v>
       </c>
       <c r="F247" t="n">
-        <v>-0.1797</v>
+        <v>-0.0078</v>
       </c>
       <c r="G247" t="n">
-        <v>-0.2702</v>
+        <v>-0.0092</v>
       </c>
       <c r="H247" t="n">
-        <v>0.0364</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
@@ -7849,7 +7849,7 @@
         <v>5</v>
       </c>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -7860,13 +7860,13 @@
         <v>96</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.1944</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="G248" t="n">
-        <v>-0.3162</v>
+        <v>-0.0837</v>
       </c>
       <c r="H248" t="n">
-        <v>0.0451</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -7879,7 +7879,7 @@
         <v>5</v>
       </c>
       <c r="C249" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -7890,13 +7890,13 @@
         <v>96</v>
       </c>
       <c r="F249" t="n">
-        <v>-0.1354</v>
+        <v>-0.125</v>
       </c>
       <c r="G249" t="n">
-        <v>-0.2738</v>
+        <v>-0.2003</v>
       </c>
       <c r="H249" t="n">
-        <v>0.0451</v>
+        <v>0.306</v>
       </c>
     </row>
     <row r="250">
@@ -7909,7 +7909,7 @@
         <v>5</v>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -7920,13 +7920,13 @@
         <v>96</v>
       </c>
       <c r="F250" t="n">
-        <v>-0.041</v>
+        <v>-0.0028</v>
       </c>
       <c r="G250" t="n">
-        <v>-0.2123</v>
+        <v>-0.0127</v>
       </c>
       <c r="H250" t="n">
-        <v>0.2172</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -7939,7 +7939,7 @@
         <v>5</v>
       </c>
       <c r="C251" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -7950,13 +7950,13 @@
         <v>96</v>
       </c>
       <c r="F251" t="n">
-        <v>-0.021</v>
+        <v>0.0377</v>
       </c>
       <c r="G251" t="n">
-        <v>-0.0512</v>
+        <v>0.0935</v>
       </c>
       <c r="H251" t="n">
-        <v>0.7514999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
@@ -7969,7 +7969,7 @@
         <v>5</v>
       </c>
       <c r="C252" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -7980,13 +7980,13 @@
         <v>96</v>
       </c>
       <c r="F252" t="n">
-        <v>-0.2979</v>
+        <v>-0.0646</v>
       </c>
       <c r="G252" t="n">
-        <v>-0.3585</v>
+        <v>-0.0766</v>
       </c>
       <c r="H252" t="n">
-        <v>0.0091</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -7999,7 +7999,7 @@
         <v>5</v>
       </c>
       <c r="C253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -8010,13 +8010,13 @@
         <v>96</v>
       </c>
       <c r="F253" t="n">
-        <v>-0.174</v>
+        <v>-0.0925</v>
       </c>
       <c r="G253" t="n">
-        <v>-0.2907</v>
+        <v>-0.1455</v>
       </c>
       <c r="H253" t="n">
-        <v>0.0451</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
@@ -8029,7 +8029,7 @@
         <v>5</v>
       </c>
       <c r="C254" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -8040,13 +8040,13 @@
         <v>96</v>
       </c>
       <c r="F254" t="n">
-        <v>-0.2262</v>
+        <v>-0.236</v>
       </c>
       <c r="G254" t="n">
-        <v>-0.3801</v>
+        <v>-0.3628</v>
       </c>
       <c r="H254" t="n">
-        <v>0.0056</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="255">
@@ -8059,7 +8059,7 @@
         <v>5</v>
       </c>
       <c r="C255" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -8070,13 +8070,13 @@
         <v>96</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.1311</v>
+        <v>-0.2057</v>
       </c>
       <c r="G255" t="n">
-        <v>-0.249</v>
+        <v>-0.3413</v>
       </c>
       <c r="H255" t="n">
-        <v>0.1321</v>
+        <v>0.0114</v>
       </c>
     </row>
     <row r="256">
@@ -8089,7 +8089,7 @@
         <v>5</v>
       </c>
       <c r="C256" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -8100,13 +8100,13 @@
         <v>96</v>
       </c>
       <c r="F256" t="n">
-        <v>-0.1497</v>
+        <v>-0.1797</v>
       </c>
       <c r="G256" t="n">
-        <v>-0.2363</v>
+        <v>-0.2702</v>
       </c>
       <c r="H256" t="n">
-        <v>0.0974</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="257">
@@ -8119,7 +8119,7 @@
         <v>5</v>
       </c>
       <c r="C257" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -8130,13 +8130,13 @@
         <v>96</v>
       </c>
       <c r="F257" t="n">
-        <v>-0.1476</v>
+        <v>-0.1944</v>
       </c>
       <c r="G257" t="n">
-        <v>-0.2352</v>
+        <v>-0.3162</v>
       </c>
       <c r="H257" t="n">
-        <v>0.1082</v>
+        <v>0.0451</v>
       </c>
     </row>
     <row r="258">
@@ -8149,7 +8149,7 @@
         <v>5</v>
       </c>
       <c r="C258" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -8160,13 +8160,13 @@
         <v>96</v>
       </c>
       <c r="F258" t="n">
-        <v>-0.0417</v>
+        <v>-0.1354</v>
       </c>
       <c r="G258" t="n">
-        <v>-0.0852</v>
+        <v>-0.2738</v>
       </c>
       <c r="H258" t="n">
-        <v>1</v>
+        <v>0.0451</v>
       </c>
     </row>
     <row r="259">
@@ -8179,7 +8179,7 @@
         <v>5</v>
       </c>
       <c r="C259" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -8190,13 +8190,13 @@
         <v>96</v>
       </c>
       <c r="F259" t="n">
-        <v>-0.0278</v>
+        <v>-0.041</v>
       </c>
       <c r="G259" t="n">
-        <v>-0.1296</v>
+        <v>-0.2123</v>
       </c>
       <c r="H259" t="n">
-        <v>0.7248</v>
+        <v>0.2172</v>
       </c>
     </row>
     <row r="260">
@@ -8209,7 +8209,7 @@
         <v>5</v>
       </c>
       <c r="C260" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -8220,13 +8220,13 @@
         <v>96</v>
       </c>
       <c r="F260" t="n">
-        <v>0.004</v>
+        <v>-0.021</v>
       </c>
       <c r="G260" t="n">
-        <v>0.0101</v>
+        <v>-0.0512</v>
       </c>
       <c r="H260" t="n">
-        <v>1</v>
+        <v>0.7514999999999999</v>
       </c>
     </row>
     <row r="261">
@@ -8239,7 +8239,7 @@
         <v>5</v>
       </c>
       <c r="C261" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -8250,13 +8250,13 @@
         <v>96</v>
       </c>
       <c r="F261" t="n">
-        <v>-0.3396</v>
+        <v>-0.2979</v>
       </c>
       <c r="G261" t="n">
-        <v>-0.4176</v>
+        <v>-0.3585</v>
       </c>
       <c r="H261" t="n">
-        <v>0.0005</v>
+        <v>0.0091</v>
       </c>
     </row>
     <row r="262">
@@ -8269,7 +8269,7 @@
         <v>5</v>
       </c>
       <c r="C262" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -8280,13 +8280,13 @@
         <v>96</v>
       </c>
       <c r="F262" t="n">
-        <v>-0.1127</v>
+        <v>-0.174</v>
       </c>
       <c r="G262" t="n">
-        <v>-0.216</v>
+        <v>-0.2907</v>
       </c>
       <c r="H262" t="n">
-        <v>0.6085</v>
+        <v>0.0451</v>
       </c>
     </row>
     <row r="263">
@@ -8299,7 +8299,7 @@
         <v>5</v>
       </c>
       <c r="C263" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -8310,13 +8310,13 @@
         <v>96</v>
       </c>
       <c r="F263" t="n">
-        <v>-0.2189</v>
+        <v>-0.2262</v>
       </c>
       <c r="G263" t="n">
-        <v>-0.3769</v>
+        <v>-0.3801</v>
       </c>
       <c r="H263" t="n">
-        <v>0.0046</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="264">
@@ -8329,7 +8329,7 @@
         <v>5</v>
       </c>
       <c r="C264" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -8340,13 +8340,13 @@
         <v>96</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.0408</v>
+        <v>-0.1311</v>
       </c>
       <c r="G264" t="n">
-        <v>-0.0736</v>
+        <v>-0.249</v>
       </c>
       <c r="H264" t="n">
-        <v>1</v>
+        <v>0.1321</v>
       </c>
     </row>
     <row r="265">
@@ -8359,7 +8359,7 @@
         <v>5</v>
       </c>
       <c r="C265" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -8370,13 +8370,13 @@
         <v>96</v>
       </c>
       <c r="F265" t="n">
-        <v>0.0195</v>
+        <v>-0.1497</v>
       </c>
       <c r="G265" t="n">
-        <v>0.032</v>
+        <v>-0.2363</v>
       </c>
       <c r="H265" t="n">
-        <v>1</v>
+        <v>0.0974</v>
       </c>
     </row>
     <row r="266">
@@ -8389,7 +8389,7 @@
         <v>5</v>
       </c>
       <c r="C266" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -8400,13 +8400,13 @@
         <v>96</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.0868</v>
+        <v>-0.1476</v>
       </c>
       <c r="G266" t="n">
-        <v>-0.1769</v>
+        <v>-0.2352</v>
       </c>
       <c r="H266" t="n">
-        <v>0.5334</v>
+        <v>0.1082</v>
       </c>
     </row>
     <row r="267">
@@ -8419,7 +8419,7 @@
         <v>5</v>
       </c>
       <c r="C267" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -8430,10 +8430,10 @@
         <v>96</v>
       </c>
       <c r="F267" t="n">
-        <v>-0.0104</v>
+        <v>-0.0417</v>
       </c>
       <c r="G267" t="n">
-        <v>-0.0239</v>
+        <v>-0.0852</v>
       </c>
       <c r="H267" t="n">
         <v>1</v>
@@ -8449,7 +8449,7 @@
         <v>5</v>
       </c>
       <c r="C268" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -8460,13 +8460,13 @@
         <v>96</v>
       </c>
       <c r="F268" t="n">
-        <v>0.0073</v>
+        <v>-0.0278</v>
       </c>
       <c r="G268" t="n">
-        <v>0.042</v>
+        <v>-0.1296</v>
       </c>
       <c r="H268" t="n">
-        <v>1</v>
+        <v>0.7248</v>
       </c>
     </row>
     <row r="269">
@@ -8479,7 +8479,7 @@
         <v>5</v>
       </c>
       <c r="C269" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -8490,10 +8490,10 @@
         <v>96</v>
       </c>
       <c r="F269" t="n">
-        <v>-0.0253</v>
+        <v>0.004</v>
       </c>
       <c r="G269" t="n">
-        <v>-0.058</v>
+        <v>0.0101</v>
       </c>
       <c r="H269" t="n">
         <v>1</v>
@@ -8509,7 +8509,7 @@
         <v>5</v>
       </c>
       <c r="C270" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -8520,13 +8520,13 @@
         <v>96</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.2729</v>
+        <v>-0.3396</v>
       </c>
       <c r="G270" t="n">
-        <v>-0.3641</v>
+        <v>-0.4176</v>
       </c>
       <c r="H270" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="271">
@@ -8539,7 +8539,7 @@
         <v>5</v>
       </c>
       <c r="C271" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -8550,13 +8550,553 @@
         <v>96</v>
       </c>
       <c r="F271" t="n">
+        <v>-0.1127</v>
+      </c>
+      <c r="G271" t="n">
+        <v>-0.216</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0.6085</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>5</v>
+      </c>
+      <c r="C272" t="n">
+        <v>5</v>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>96</v>
+      </c>
+      <c r="F272" t="n">
+        <v>-0.2189</v>
+      </c>
+      <c r="G272" t="n">
+        <v>-0.3769</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0.0046</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>5</v>
+      </c>
+      <c r="C273" t="n">
+        <v>5</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>WAI-SR</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>96</v>
+      </c>
+      <c r="F273" t="n">
+        <v>-0.0408</v>
+      </c>
+      <c r="G273" t="n">
+        <v>-0.0736</v>
+      </c>
+      <c r="H273" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>5</v>
+      </c>
+      <c r="C274" t="n">
+        <v>5</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>CSQ-8</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>96</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="H274" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>5</v>
+      </c>
+      <c r="C275" t="n">
+        <v>5</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>MI-SAT</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>96</v>
+      </c>
+      <c r="F275" t="n">
+        <v>-0.0868</v>
+      </c>
+      <c r="G275" t="n">
+        <v>-0.1769</v>
+      </c>
+      <c r="H275" t="n">
+        <v>0.5334</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>5</v>
+      </c>
+      <c r="C276" t="n">
+        <v>5</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>MITI</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>96</v>
+      </c>
+      <c r="F276" t="n">
+        <v>-0.0104</v>
+      </c>
+      <c r="G276" t="n">
+        <v>-0.0239</v>
+      </c>
+      <c r="H276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>5</v>
+      </c>
+      <c r="C277" t="n">
+        <v>5</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>96</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="H277" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>5</v>
+      </c>
+      <c r="C278" t="n">
+        <v>5</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>MICI</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>96</v>
+      </c>
+      <c r="F278" t="n">
+        <v>-0.0253</v>
+      </c>
+      <c r="G278" t="n">
+        <v>-0.058</v>
+      </c>
+      <c r="H278" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>5</v>
+      </c>
+      <c r="C279" t="n">
+        <v>5</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>96</v>
+      </c>
+      <c r="F279" t="n">
+        <v>-0.2729</v>
+      </c>
+      <c r="G279" t="n">
+        <v>-0.3641</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>5</v>
+      </c>
+      <c r="C280" t="n">
+        <v>5</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>96</v>
+      </c>
+      <c r="F280" t="n">
         <v>-0.1648</v>
       </c>
-      <c r="G271" t="n">
+      <c r="G280" t="n">
         <v>-0.3042</v>
       </c>
-      <c r="H271" t="n">
+      <c r="H280" t="n">
         <v>0.0275</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>5</v>
+      </c>
+      <c r="C281" t="n">
+        <v>6</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>96</v>
+      </c>
+      <c r="F281" t="n">
+        <v>-0.3966</v>
+      </c>
+      <c r="G281" t="n">
+        <v>-0.5991</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>5</v>
+      </c>
+      <c r="C282" t="n">
+        <v>6</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>WAI-SR</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>96</v>
+      </c>
+      <c r="F282" t="n">
+        <v>-0.2092</v>
+      </c>
+      <c r="G282" t="n">
+        <v>-0.3578</v>
+      </c>
+      <c r="H282" t="n">
+        <v>0.0028</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>5</v>
+      </c>
+      <c r="C283" t="n">
+        <v>6</v>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>CSQ-8</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>96</v>
+      </c>
+      <c r="F283" t="n">
+        <v>-0.224</v>
+      </c>
+      <c r="G283" t="n">
+        <v>-0.3327</v>
+      </c>
+      <c r="H283" t="n">
+        <v>0.0106</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>5</v>
+      </c>
+      <c r="C284" t="n">
+        <v>6</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>MI-SAT</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>96</v>
+      </c>
+      <c r="F284" t="n">
+        <v>-0.2535</v>
+      </c>
+      <c r="G284" t="n">
+        <v>-0.3962</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0.0014</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>5</v>
+      </c>
+      <c r="C285" t="n">
+        <v>6</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>MITI</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>96</v>
+      </c>
+      <c r="F285" t="n">
+        <v>-0.2969</v>
+      </c>
+      <c r="G285" t="n">
+        <v>-0.5578</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>5</v>
+      </c>
+      <c r="C286" t="n">
+        <v>6</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>96</v>
+      </c>
+      <c r="F286" t="n">
+        <v>-0.0623</v>
+      </c>
+      <c r="G286" t="n">
+        <v>-0.2968</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0.0111</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>5</v>
+      </c>
+      <c r="C287" t="n">
+        <v>6</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>MICI</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>96</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0.1589</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>5</v>
+      </c>
+      <c r="C288" t="n">
+        <v>6</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>96</v>
+      </c>
+      <c r="F288" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="G288" t="n">
+        <v>-0.5925</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>claude-haiku-4-5</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>5</v>
+      </c>
+      <c r="C289" t="n">
+        <v>6</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>96</v>
+      </c>
+      <c r="F289" t="n">
+        <v>-0.3431</v>
+      </c>
+      <c r="G289" t="n">
+        <v>-0.5377</v>
+      </c>
+      <c r="H289" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8930,7 +9470,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -8941,13 +9481,13 @@
         <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1869</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3244</v>
+        <v>0.1329</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -8963,7 +9503,7 @@
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -8974,13 +9514,13 @@
         <v>96</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0946</v>
+        <v>-0.0069</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1691</v>
+        <v>-0.0125</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0645</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -8996,7 +9536,7 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -9007,13 +9547,13 @@
         <v>96</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0326</v>
+        <v>0.0182</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0516</v>
+        <v>0.0314</v>
       </c>
       <c r="I13" t="n">
-        <v>0.424</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -9029,7 +9569,7 @@
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -9040,13 +9580,13 @@
         <v>96</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0885</v>
+        <v>0.0278</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1125</v>
+        <v>0.0372</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2821</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -9062,7 +9602,7 @@
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -9073,13 +9613,13 @@
         <v>96</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1745</v>
+        <v>0.0078</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2849</v>
+        <v>0.0127</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0097</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -9095,7 +9635,7 @@
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -9106,13 +9646,13 @@
         <v>96</v>
       </c>
       <c r="G16" t="n">
-        <v>0.024</v>
+        <v>0.0127</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1096</v>
+        <v>0.0648</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09959999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -9128,7 +9668,7 @@
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -9139,13 +9679,13 @@
         <v>96</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0413</v>
+        <v>-0.0176</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.149</v>
+        <v>-0.0755</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1351</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -9161,7 +9701,7 @@
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -9172,13 +9712,13 @@
         <v>96</v>
       </c>
       <c r="G18" t="n">
-        <v>0.125</v>
+        <v>0.025</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1781</v>
+        <v>0.0371</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06560000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -9194,7 +9734,7 @@
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -9205,13 +9745,13 @@
         <v>96</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2488</v>
+        <v>0.1305</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5063</v>
+        <v>0.2395</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.1121</v>
       </c>
     </row>
     <row r="20">
@@ -9524,7 +10064,7 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -9535,13 +10075,13 @@
         <v>96</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0624</v>
+        <v>-0.168</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1136</v>
+        <v>-0.3524</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="30">
@@ -9557,7 +10097,7 @@
         <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -9568,13 +10108,13 @@
         <v>96</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.0017</v>
+        <v>-0.1519</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0029</v>
+        <v>-0.2655</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="31">
@@ -9590,7 +10130,7 @@
         <v>7</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -9601,13 +10141,13 @@
         <v>96</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0378</v>
+        <v>-0.1016</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0587</v>
+        <v>-0.1749</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0.3284</v>
       </c>
     </row>
     <row r="32">
@@ -9623,7 +10163,7 @@
         <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -9634,13 +10174,13 @@
         <v>96</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.0035</v>
+        <v>-0.1389</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0052</v>
+        <v>-0.2134</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0.2127</v>
       </c>
     </row>
     <row r="33">
@@ -9656,7 +10196,7 @@
         <v>7</v>
       </c>
       <c r="D33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -9667,13 +10207,13 @@
         <v>96</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0286</v>
+        <v>-0.1302</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0693</v>
+        <v>-0.2646</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="34">
@@ -9689,7 +10229,7 @@
         <v>7</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -9700,13 +10240,13 @@
         <v>96</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0095</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.0382</v>
+        <v>-0.2781</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.0293</v>
       </c>
     </row>
     <row r="35">
@@ -9722,7 +10262,7 @@
         <v>7</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -9733,13 +10273,13 @@
         <v>96</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0659</v>
+        <v>0.0056</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2117</v>
+        <v>0.0165</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4381</v>
+        <v>0.7893</v>
       </c>
     </row>
     <row r="36">
@@ -9755,7 +10295,7 @@
         <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -9766,13 +10306,13 @@
         <v>96</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1021</v>
+        <v>-0.1896</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.1347</v>
+        <v>-0.2803</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.0285</v>
       </c>
     </row>
     <row r="37">
@@ -9788,7 +10328,7 @@
         <v>7</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -9799,13 +10339,13 @@
         <v>96</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0227</v>
+        <v>-0.1464</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.043</v>
+        <v>-0.3246</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0.0073</v>
       </c>
     </row>
   </sheetData>
